--- a/Config/Datas/Tables/w_物品_ItemConfig.xlsx
+++ b/Config/Datas/Tables/w_物品_ItemConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbItem" sheetId="1" r:id="Rc955fdbe38884b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbItem" sheetId="1" r:id="Re81ee23765884f1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,68 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -95,8 +155,28 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -158,11 +238,25 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="73">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -256,6 +350,122 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -458,65 +668,71 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="25" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="52" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="52" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="52" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="D1" s="52" t="str">
         <x:v>iconResourceId</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="29" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="54" t="str">
         <x:v>##type</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B2" s="54" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
+      <x:c r="C2" s="54" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="D2" s="54" t="str">
         <x:v>int?#ref=TbResource</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="30" t="str">
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="57" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B3" s="16"/>
-      <x:c r="C3" s="16"/>
-      <x:c r="D3" s="16"/>
+      <x:c r="B3" s="58"/>
+      <x:c r="C3" s="58"/>
+      <x:c r="D3" s="58"/>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="31" t="str">
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="61" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B4" s="23" t="str">
+      <x:c r="B4" s="62" t="str">
         <x:v>物品ID</x:v>
       </x:c>
-      <x:c r="C4" s="23" t="str">
+      <x:c r="C4" s="62" t="str">
         <x:v>显示名称</x:v>
       </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>图标资源ID；无需求前保持空表</x:v>
+      <x:c r="D4" s="62" t="str">
+        <x:v>图标资源ID；功能资源完成后填写</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="32"/>
-      <x:c r="D5" s="32"/>
+      <x:c r="A5" s="71"/>
+      <x:c r="B5" s="72" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="C5" s="71" t="str">
+        <x:v>经验</x:v>
+      </x:c>
+      <x:c r="D5" s="72"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
